--- a/RUNBOOK.xlsx
+++ b/RUNBOOK.xlsx
@@ -17,7 +17,7 @@
     <t>Attachment Reader — Production Deploy Runbook</t>
   </si>
   <si>
-    <t>Generated: 2026-09-03 05:02 UTC</t>
+    <t>Generated: 2026-09-03 06:11 UTC</t>
   </si>
   <si>
     <t>#</t>
@@ -225,13 +225,13 @@
     <t>Mitigation</t>
   </si>
   <si>
-    <t>Image OCR — confirmed working (2026-09-03)</t>
-  </si>
-  <si>
-    <t>Correctly OCR'd a PNG screenshot on a live issue in a real Forge deploy. Was a real risk going in: tesseract.js's Node build spawns a worker_threads.Worker at a separate file path and loads its WASM engine via a runtime fs.readFileSync() — both reached dynamically, not through Forge's static single-file bundle graph. Evidently bundles/runs fine in practice.</t>
-  </si>
-  <si>
-    <t>Spot-check an image attachment after deploying to each new app registration or environment (bundler/runtime specifics could differ across accounts or future CLI versions); check forge logs for worker/WASM load failures if one ever comes back empty.</t>
+    <t>Image OCR — bundling failure, refixed, needs redeploy to confirm</t>
+  </si>
+  <si>
+    <t>Two real, distinct __dirname-based path failures hit in production (tesseract.js's own workerPath default, then our own import.meta.url-based override) proved Forge's bundler preserves no module's real self-location. An earlier 'confirmed working' note was based on a chat success that was likely Rovo's native image-viewing, not this action.</t>
+  </si>
+  <si>
+    <t>Fixed by never computing a path to an existing file: gen_ocr_assets.mjs embeds a custom worker bundle + WASM core + trained data as base64; index.js writes them to os.tmpdir() at call time and spawns from there. Validated locally end-to-end (PNG+JPEG) but NOT yet confirmed on a real Forge deploy — redeploy and re-test before trusting it.</t>
   </si>
   <si>
     <t>Image size / OCR timeout</t>

--- a/RUNBOOK.xlsx
+++ b/RUNBOOK.xlsx
@@ -17,7 +17,7 @@
     <t>Attachment Reader — Production Deploy Runbook</t>
   </si>
   <si>
-    <t>Generated: 2026-09-03 06:11 UTC</t>
+    <t>Generated: 2026-09-03 06:51 UTC</t>
   </si>
   <si>
     <t>#</t>
@@ -225,13 +225,13 @@
     <t>Mitigation</t>
   </si>
   <si>
-    <t>Image OCR — bundling failure, refixed, needs redeploy to confirm</t>
-  </si>
-  <si>
-    <t>Two real, distinct __dirname-based path failures hit in production (tesseract.js's own workerPath default, then our own import.meta.url-based override) proved Forge's bundler preserves no module's real self-location. An earlier 'confirmed working' note was based on a chat success that was likely Rovo's native image-viewing, not this action.</t>
-  </si>
-  <si>
-    <t>Fixed by never computing a path to an existing file: gen_ocr_assets.mjs embeds a custom worker bundle + WASM core + trained data as base64; index.js writes them to os.tmpdir() at call time and spawns from there. Validated locally end-to-end (PNG+JPEG) but NOT yet confirmed on a real Forge deploy — redeploy and re-test before trusting it.</t>
+    <t>Image OCR — confirmed working (2026-09-03), via Jira Automation</t>
+  </si>
+  <si>
+    <t>Second 'confirmed working' note on this risk — the first was wrong (chat success was likely Rovo's native image-viewing). This time confirmed via the Automation-triggered path itself: attachment 10146 read back real structured content (scan tool, severities, branch name), not just a bare PASS. Took two distinct __dirname-based path failures in production to get here (tesseract.js's own workerPath default, then our own import.meta.url-based override), proving Forge's bundler preserves no module's real self-location.</t>
+  </si>
+  <si>
+    <t>Fixed by never computing a path to an existing file: gen_ocr_assets.mjs embeds a custom worker bundle + WASM core + trained data as base64; index.js writes them to os.tmpdir() at call time and spawns from there. PNG and JPEG both confirmed.</t>
   </si>
   <si>
     <t>Image size / OCR timeout</t>
